--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0203.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0203.xlsx
@@ -21894,7 +21894,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Ta bảo ngươi rồi, bức tượng chúng ta giao có gì đó rất sai sai...</t>
+          <t>Tao bảo mày rồi, bức tượng chúng ta giao có gì đó rất sai sai...</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Ồ, xin chào {Male=chàng trai trẻ đẹp trai;Female=cô gái trẻ xinh đẹp} nhé. Có muốn để lại dấu ấn trong chiếc máy giao dịch nhỏ của ta không?</t>
+          <t>Ồ, xin chào {Male=handsome young man;Female=beautiful young lady} nhé. Có muốn để lại dấu ấn trong chiếc máy giao dịch nhỏ của ta không?</t>
         </is>
       </c>
     </row>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Làm việc ở đây sợ muốn chết luôn. Ta nghỉ... Ta phải nghỉ thôi...</t>
+          <t>Làm việc ở đây sợ muốn chết luôn. Tao nghỉ... Tao phải nghỉ thôi...</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Sau bao năm trời, lẽ ra cũng phải có một cái thành công chứ. Thực sự thì ta cũng hơi tò mò xem cái đó rốt cuộc là cái gì.</t>
+          <t>Sau bao năm trời, lẽ ra cũng phải có một cái thành công chứ. Thực sự thì tao cũng hơi tò mò xem cái đó rốt cuộc là cái gì.</t>
         </is>
       </c>
     </row>
